--- a/api/templates/error_rate/uk.xlsx
+++ b/api/templates/error_rate/uk.xlsx
@@ -238,12 +238,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -654,7 +655,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -663,77 +664,77 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" ht="39.75" customHeight="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="39.75" customHeight="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -768,42 +769,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="39.75" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" ht="39.75" customHeight="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
+      <c r="A9" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -853,7 +854,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -862,61 +863,61 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" ht="39.75" customHeight="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="39.75" customHeight="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="11" t="s">
         <v>24</v>
       </c>
     </row>

--- a/api/templates/error_rate/uk.xlsx
+++ b/api/templates/error_rate/uk.xlsx
@@ -33,7 +33,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Виведені з експлуатації пристрої: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -238,13 +238,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -655,7 +654,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -664,77 +663,77 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" ht="39.75" customHeight="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" ht="39.75" customHeight="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -769,42 +768,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="39.75" customHeight="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="5" ht="39.75" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
+      <c r="A9" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -854,7 +853,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -863,61 +862,61 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" ht="39.75" customHeight="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" ht="39.75" customHeight="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="10" t="s">
         <v>24</v>
       </c>
     </row>
